--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,162 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Goal_NoGoal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:19</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Argentina - Francia</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:19</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Italia - Stati Uniti</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brasile - Giappone</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>GOAL</t>
         </is>
       </c>
     </row>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 17:19</t>
+          <t>16/06/2026 17:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16/06/2026 17:19</t>
+          <t>16/06/2026 17:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16/06/2026 17:19</t>
+          <t>16/06/2026 17:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FIFA World Cup</t>
+          <t>Palinsesto</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 17:22</t>
+          <t>16/06/2026 19:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Argentina - Francia</t>
+          <t>Nessun match in palinsesto dal provider reale per oggi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -527,110 +527,6 @@
         </is>
       </c>
       <c r="J2" t="inlineStr">
-        <is>
-          <t>GOAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>16/06/2026 17:22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Italia - Stati Uniti</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>OVER 2.5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>GOAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>16/06/2026 17:22</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Brasile - Giappone</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>OVER 2.5</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>GOAL</t>
         </is>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 19:58</t>
+          <t>16/06/2026 20:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nessun match in palinsesto dal provider reale per oggi</t>
+          <t>Nessun match in palinsesto nei prossimi 4 giorni</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,17 +483,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Palinsesto</t>
+          <t>FIFA World Cup</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 20:14</t>
+          <t>16/06/2026 20:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nessun match in palinsesto nei prossimi 4 giorni</t>
+          <t>Germania - Spagna</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -527,6 +527,110 @@
         </is>
       </c>
       <c r="J2" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Francia - Portogallo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Italia - Argentina</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>GOAL</t>
         </is>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 20:24</t>
+          <t>16/06/2026 22:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Germania - Spagna</t>
+          <t>Iraq - Norway</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -540,12 +540,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16/06/2026 20:24</t>
+          <t>17/06/2026 01:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Francia - Portogallo</t>
+          <t>Argentina - Algeria</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16/06/2026 20:24</t>
+          <t>17/06/2026 04:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italia - Argentina</t>
+          <t>Austria - Jordan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -631,6 +631,734 @@
         </is>
       </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>17/06/2026 17:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Portugal - Congo DR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>England - Croatia</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17/06/2026 23:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ghana - Panama</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18/06/2026 02:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Uzbekistan - Colombia</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18/06/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Czechia - South Africa</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>18/06/2026 19:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Switzerland - Bosnia-Herzegovina</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18/06/2026 22:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Canada - Qatar</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19/06/2026 01:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mexico - South Korea</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>19/06/2026 19:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>United States - Australia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19/06/2026 22:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Scotland - Morocco</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20/06/2026 00:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brazil - Haiti</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20/06/2026 03:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Turkey - Paraguay</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20/06/2026 17:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Netherlands - Sweden</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>GOAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20/06/2026 20:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Germany - Ivory Coast</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>GOAL</t>
         </is>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,37 +446,72 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Punti_Casa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Punti_Trasferta</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Media_Goal_Casa</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Media_Goal_Trasferta</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Risultato_Esatto</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Doppia_Chance</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>U/O_1.5</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>U/O_2.5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>U/O_3.5</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Goal_NoGoal</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>DC+U/O2.5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Corner_1X2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Odds_1X2</t>
         </is>
       </c>
     </row>
@@ -488,47 +523,74 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 22:00</t>
+          <t>17/06/2026 03:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Iraq - Norway</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>Argentina - Algeria</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -540,47 +602,74 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17/06/2026 01:00</t>
+          <t>17/06/2026 06:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Argentina - Algeria</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>Austria - Jordan</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -592,47 +681,74 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17/06/2026 04:00</t>
+          <t>17/06/2026 19:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austria - Jordan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>Portugal - Congo DR</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -644,47 +760,74 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17/06/2026 17:00</t>
+          <t>17/06/2026 22:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal - Congo DR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>England - Croatia</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -696,47 +839,74 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17/06/2026 20:00</t>
+          <t>18/06/2026 01:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England - Croatia</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>Ghana - Panama</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -748,47 +918,74 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17/06/2026 23:00</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ghana - Panama</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>Uzbekistan - Colombia</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -800,47 +997,74 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18/06/2026 02:00</t>
+          <t>18/06/2026 18:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan - Colombia</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>Czechia - South Africa</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -852,47 +1076,74 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18/06/2026 16:00</t>
+          <t>18/06/2026 21:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>Switzerland - Bosnia-Herzegovina</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -904,47 +1155,74 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18/06/2026 19:00</t>
+          <t>19/06/2026 00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>Canada - Qatar</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -956,47 +1234,74 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18/06/2026 22:00</t>
+          <t>19/06/2026 03:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>Mexico - South Korea</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1313,74 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19/06/2026 01:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>United States - Australia</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1060,47 +1392,74 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19/06/2026 19:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>Scotland - Morocco</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1112,47 +1471,74 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19/06/2026 22:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>Brazil - Haiti</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1164,47 +1550,74 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20/06/2026 00:30</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>Turkey - Paraguay</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1216,47 +1629,74 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20/06/2026 03:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>Netherlands - Sweden</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>GOAL</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1268,99 +1708,74 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20/06/2026 17:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>Germany - Ivory Coast</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>OVER 2.5</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>GOAL</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>20/06/2026 20:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Germany - Ivory Coast</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>OVER 2.5</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>GOAL</t>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,16 @@
           <t>Odds_1X2</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>PRONOSTICO</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>U/O 2.5</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -537,11 +547,15 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -550,7 +564,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +579,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -575,22 +589,32 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -616,11 +640,15 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -629,7 +657,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -644,7 +672,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -654,22 +682,32 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -695,11 +733,15 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -708,7 +750,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -723,7 +765,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -733,22 +775,32 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -774,11 +826,15 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -787,7 +843,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -802,7 +858,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -812,22 +868,32 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -853,11 +919,15 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -866,7 +936,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -881,7 +951,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -891,22 +961,32 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -932,11 +1012,15 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -945,7 +1029,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -960,7 +1044,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -970,22 +1054,32 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1011,11 +1105,15 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1024,7 +1122,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1039,7 +1137,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1049,22 +1147,32 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1090,11 +1198,15 @@
       <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1103,7 +1215,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1118,7 +1230,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1128,22 +1240,32 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1169,11 +1291,15 @@
       <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1182,7 +1308,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1197,7 +1323,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1207,22 +1333,32 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1248,11 +1384,15 @@
       <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1261,7 +1401,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1276,7 +1416,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1286,22 +1426,32 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1327,11 +1477,15 @@
       <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1340,7 +1494,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1355,7 +1509,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1365,22 +1519,32 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1406,11 +1570,15 @@
       <c r="E13" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1419,7 +1587,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1434,7 +1602,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1444,22 +1612,32 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1485,11 +1663,15 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1498,7 +1680,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1513,7 +1695,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1523,22 +1705,32 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1564,11 +1756,15 @@
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1577,7 +1773,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1592,7 +1788,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1602,22 +1798,32 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1643,11 +1849,15 @@
       <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1656,7 +1866,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1671,7 +1881,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1681,22 +1891,32 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1722,11 +1942,15 @@
       <c r="E17" t="n">
         <v>3</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1.13 xG</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.95 xG</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1735,7 +1959,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1750,7 +1974,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1760,22 +1984,32 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>GOAL</t>
+          <t>NOGOAL</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>1X+UNDER</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,16 +514,6 @@
           <t>Odds_1X2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>PRONOSTICO</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>U/O 2.5</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -533,12 +523,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17/06/2026 03:00</t>
+          <t>17/06/2026 22:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Argentina - Algeria</t>
+          <t>England - Croatia</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -549,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,16 +595,6 @@
       <c r="Q2" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -626,12 +606,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17/06/2026 06:00</t>
+          <t>18/06/2026 01:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austria - Jordan</t>
+          <t>Ghana - Panama</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -642,12 +622,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,16 +678,6 @@
       <c r="Q3" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -719,12 +689,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17/06/2026 19:00</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portugal - Congo DR</t>
+          <t>Uzbekistan - Colombia</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -735,12 +705,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -791,16 +761,6 @@
       <c r="Q4" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -812,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>18/06/2026 18:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England - Croatia</t>
+          <t>Czechia - South Africa</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -828,12 +788,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -884,16 +844,6 @@
       <c r="Q5" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -905,28 +855,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18/06/2026 01:00</t>
+          <t>18/06/2026 21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ghana - Panama</t>
+          <t>Switzerland - Bosnia-Herzegovina</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -977,16 +927,6 @@
       <c r="Q6" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -998,28 +938,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>19/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan - Colombia</t>
+          <t>Canada - Qatar</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1070,16 +1010,6 @@
       <c r="Q7" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1091,28 +1021,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>19/06/2026 03:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
+          <t>Mexico - South Korea</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1163,16 +1093,6 @@
       <c r="Q8" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1184,28 +1104,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18/06/2026 21:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
+          <t>United States - Australia</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1256,16 +1176,6 @@
       <c r="Q9" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1277,28 +1187,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19/06/2026 00:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
+          <t>Scotland - Morocco</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1349,16 +1259,6 @@
       <c r="Q10" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1370,28 +1270,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19/06/2026 03:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
+          <t>Brazil - Haiti</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1442,16 +1342,6 @@
       <c r="Q11" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1463,28 +1353,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Turkey - Paraguay</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1535,16 +1425,6 @@
       <c r="Q12" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1556,28 +1436,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1628,16 +1508,6 @@
       <c r="Q13" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1649,28 +1519,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1721,16 +1591,6 @@
       <c r="Q14" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1602,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1758,12 +1618,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1814,16 +1674,6 @@
       <c r="Q15" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1835,28 +1685,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1907,16 +1757,6 @@
       <c r="Q16" t="inlineStr">
         <is>
           <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
         </is>
       </c>
     </row>
@@ -1928,28 +1768,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.13 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.95 xG</t>
+          <t>0-1 MG</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2002,14 +1842,170 @@
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21/06/2026 21:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Belgium - Iran</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Uruguay - Cape Verde Islands</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -523,12 +523,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>18/06/2026 18:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>England - Croatia</t>
+          <t>Czechia - South Africa</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -606,19 +606,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18/06/2026 01:00</t>
+          <t>18/06/2026 21:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ghana - Panama</t>
+          <t>Switzerland - Bosnia-Herzegovina</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -689,19 +689,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>19/06/2026 00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan - Colombia</t>
+          <t>Canada - Qatar</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -772,19 +772,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>19/06/2026 03:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
+          <t>Mexico - South Korea</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -855,19 +855,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18/06/2026 21:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
+          <t>United States - Australia</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -938,16 +938,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19/06/2026 00:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
+          <t>Scotland - Morocco</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -1021,19 +1021,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19/06/2026 03:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
+          <t>Brazil - Haiti</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1104,19 +1104,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Turkey - Paraguay</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1187,19 +1187,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1270,19 +1270,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1436,19 +1436,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
         <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1519,19 +1519,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1602,19 +1602,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1685,16 +1685,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1851,19 +1851,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,19 +1934,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,16 @@
           <t>Odds_1X2</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Pronostico_MG_Casa</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Pronostico_MG_Trasferta</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -523,29 +533,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
+          <t>United States - Australia</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -595,6 +601,16 @@
       <c r="Q2" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -606,29 +622,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18/06/2026 21:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
+          <t>Scotland - Morocco</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+      <c r="F3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -678,6 +690,16 @@
       <c r="Q3" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -689,29 +711,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19/06/2026 00:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
+          <t>Brazil - Haiti</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -761,6 +779,16 @@
       <c r="Q4" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -772,29 +800,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19/06/2026 03:00</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
+          <t>Turkey - Paraguay</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -844,6 +868,16 @@
       <c r="Q5" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -855,29 +889,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -927,6 +957,16 @@
       <c r="Q6" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -938,29 +978,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1010,6 +1046,16 @@
       <c r="Q7" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1021,29 +1067,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+      <c r="F8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1093,6 +1135,16 @@
       <c r="Q8" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1104,29 +1156,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1176,6 +1224,16 @@
       <c r="Q9" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1187,29 +1245,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1259,6 +1313,16 @@
       <c r="Q10" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1270,29 +1334,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1342,6 +1402,16 @@
       <c r="Q11" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1353,29 +1423,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1425,6 +1491,16 @@
       <c r="Q12" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1436,29 +1512,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+      <c r="F13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1508,6 +1580,16 @@
       <c r="Q13" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1519,29 +1601,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1591,6 +1669,16 @@
       <c r="Q14" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1602,29 +1690,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1674,6 +1758,16 @@
       <c r="Q15" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1685,29 +1779,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1757,6 +1847,16 @@
       <c r="Q16" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1768,29 +1868,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1840,6 +1936,16 @@
       <c r="Q17" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1851,29 +1957,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1923,6 +2025,16 @@
       <c r="Q18" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>
@@ -1934,78 +2046,173 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>24/06/2026 01:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Panama - Croatia</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
         </is>
       </c>
     </row>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,65 +461,85 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Media_Goal_Subiti_Casa</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Media_Goal_Trasferta</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Media_Goal_Subiti_Trasferta</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Forma_Casa</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Forma_Trasferta</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Risultato_Esatto</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Doppia_Chance</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>U/O_1.5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>U/O_2.5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>U/O_3.5</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Goal_NoGoal</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DC+U/O2.5</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Corner_1X2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odds_1X2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Pronostico_MG_Casa</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Pronostico_MG_Trasferta</t>
         </is>
@@ -551,64 +571,72 @@
         <v>1.2</v>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.1</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -640,64 +668,72 @@
         <v>1.2</v>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>1.1</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -729,64 +765,72 @@
         <v>1.2</v>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -818,64 +862,72 @@
         <v>1.2</v>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>1.1</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -907,64 +959,72 @@
         <v>1.2</v>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>1.1</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -996,64 +1056,72 @@
         <v>1.2</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>1.1</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -1085,64 +1153,72 @@
         <v>1.2</v>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.1</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -1174,64 +1250,72 @@
         <v>1.2</v>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>1.1</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -1263,64 +1347,72 @@
         <v>1.2</v>
       </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>1.1</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -1352,64 +1444,72 @@
         <v>1.2</v>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.1</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -1441,64 +1541,72 @@
         <v>1.2</v>
       </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
         <v>1.1</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -1530,64 +1638,72 @@
         <v>1.2</v>
       </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>1.1</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -1619,64 +1735,72 @@
         <v>1.2</v>
       </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
         <v>1.1</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -1708,64 +1832,72 @@
         <v>1.2</v>
       </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
         <v>1.1</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -1797,64 +1929,72 @@
         <v>1.2</v>
       </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.1</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -1886,64 +2026,72 @@
         <v>1.2</v>
       </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
         <v>1.1</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -1975,64 +2123,72 @@
         <v>1.2</v>
       </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
         <v>1.1</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -2064,64 +2220,72 @@
         <v>1.2</v>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
         <v>1.1</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
@@ -2153,64 +2317,72 @@
         <v>1.2</v>
       </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
         <v>1.1</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>1X</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>OVER 1.5</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>UNDER 2.5</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>UNDER 3.5</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>NOGOAL</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>1X+UNDER</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,16 +553,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -650,19 +650,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -747,16 +747,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -844,19 +844,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1.2</v>
@@ -941,19 +941,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>1.2</v>
@@ -1038,19 +1038,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>1.2</v>
@@ -1135,19 +1135,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
@@ -1232,16 +1232,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1329,19 +1329,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>1.2</v>
@@ -1426,19 +1426,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1.2</v>
@@ -1523,19 +1523,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>1.2</v>
@@ -1620,19 +1620,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>1.2</v>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1814,19 +1814,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1911,16 +1911,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>23/06/2026 02:00</t>
+          <t>24/06/2026 01:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway - Senegal</t>
+          <t>Panama - Croatia</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2008,19 +2008,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23/06/2026 05:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan - Algeria</t>
+          <t>Colombia - Congo DR</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -2105,19 +2105,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23/06/2026 19:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal - Uzbekistan</t>
+          <t>Switzerland - Canada</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -2202,19 +2202,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23/06/2026 22:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England - Ghana</t>
+          <t>Bosnia-Herzegovina - Qatar</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -2299,16 +2299,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2383,6 +2383,103 @@
         </is>
       </c>
       <c r="W20" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>25/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Scotland - Brazil</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,16 +553,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -650,19 +650,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -747,19 +747,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1.2</v>
@@ -844,16 +844,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -941,12 +941,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1232,19 +1232,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
@@ -1329,19 +1329,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>1.2</v>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1523,16 +1523,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23/06/2026 02:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway - Senegal</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1620,16 +1620,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23/06/2026 05:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan - Algeria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23/06/2026 19:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal - Uzbekistan</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1814,19 +1814,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23/06/2026 22:00</t>
+          <t>24/06/2026 01:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England - Ghana</t>
+          <t>Panama - Croatia</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1911,19 +1911,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Colombia - Congo DR</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
@@ -2008,19 +2008,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Colombia - Congo DR</t>
+          <t>Switzerland - Canada</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -2110,14 +2110,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland - Canada</t>
+          <t>Bosnia-Herzegovina - Qatar</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -2202,19 +2202,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina - Qatar</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -2304,14 +2304,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco - Haiti</t>
+          <t>Scotland - Brazil</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
         <v>4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>1.2</v>
@@ -2383,103 +2383,6 @@
         </is>
       </c>
       <c r="W20" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>25/06/2026 00:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Scotland - Brazil</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>NOGOAL</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>1X+UNDER</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>1.2</v>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,19 +553,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>1.2</v>
@@ -650,19 +650,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -747,16 +747,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -844,12 +844,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -941,12 +941,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
@@ -1232,19 +1232,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1426,16 +1426,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23/06/2026 02:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway - Senegal</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1523,16 +1523,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23/06/2026 05:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan - Algeria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1620,19 +1620,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23/06/2026 19:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal - Uzbekistan</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>1.2</v>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23/06/2026 22:00</t>
+          <t>24/06/2026 01:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England - Ghana</t>
+          <t>Panama - Croatia</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1814,19 +1814,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Colombia - Congo DR</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1911,19 +1911,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Colombia - Congo DR</t>
+          <t>Switzerland - Canada</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
@@ -2013,14 +2013,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland - Canada</t>
+          <t>Bosnia-Herzegovina - Qatar</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -2105,19 +2105,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina - Qatar</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -2207,14 +2207,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco - Haiti</t>
+          <t>Scotland - Brazil</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
         <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -2286,103 +2286,6 @@
         </is>
       </c>
       <c r="W19" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>25/06/2026 00:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Scotland - Brazil</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>NOGOAL</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>1X+UNDER</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,12 +553,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>24/06/2026 01:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Panama - Croatia</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -650,16 +650,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Colombia - Congo DR</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -747,19 +747,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Switzerland - Canada</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>1.2</v>
@@ -844,12 +844,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Bosnia-Herzegovina - Qatar</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -941,19 +941,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>1.2</v>
@@ -1038,19 +1038,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Scotland - Brazil</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>1.2</v>
@@ -1135,19 +1135,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>25/06/2026 03:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>Czechia - Mexico</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
@@ -1232,19 +1232,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>25/06/2026 03:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>South Africa - South Korea</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
@@ -1329,19 +1329,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23/06/2026 02:00</t>
+          <t>25/06/2026 22:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway - Senegal</t>
+          <t>Ecuador - Germany</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
         <v>1.2</v>
@@ -1426,19 +1426,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23/06/2026 05:00</t>
+          <t>25/06/2026 22:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan - Algeria</t>
+          <t>Curaçao - Ivory Coast</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>1.2</v>
@@ -1523,19 +1523,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23/06/2026 19:00</t>
+          <t>26/06/2026 01:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal - Uzbekistan</t>
+          <t>Tunisia - Netherlands</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>1.2</v>
@@ -1620,16 +1620,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23/06/2026 22:00</t>
+          <t>26/06/2026 01:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England - Ghana</t>
+          <t>Japan - Sweden</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Turkey - United States</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1814,19 +1814,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Colombia - Congo DR</t>
+          <t>Paraguay - Australia</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1911,19 +1911,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>26/06/2026 21:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland - Canada</t>
+          <t>Norway - France</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
@@ -2008,19 +2008,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>26/06/2026 21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina - Qatar</t>
+          <t>Senegal - Iraq</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -2105,19 +2105,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25/06/2026 00:00</t>
+          <t>27/06/2026 02:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco - Haiti</t>
+          <t>Uruguay - Spain</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
         <v>4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -2202,19 +2202,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25/06/2026 00:00</t>
+          <t>27/06/2026 02:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland - Brazil</t>
+          <t>Cape Verde Islands - Saudi Arabia</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -2286,6 +2286,588 @@
         </is>
       </c>
       <c r="W19" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>27/06/2026 05:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New Zealand - Belgium</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>27/06/2026 05:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Egypt - Iran</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>27/06/2026 23:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Panama - England</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>27/06/2026 23:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Croatia - Ghana</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>28/06/2026 01:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Colombia - Portugal</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>28/06/2026 01:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Congo DR - Uzbekistan</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>OVER 1.5</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>UNDER 3.5</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>NOGOAL</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1X+UNDER</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0-1 MG</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>

--- a/Pronostici_App_Betting.xlsx
+++ b/Pronostici_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,16 +553,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -650,19 +650,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Colombia - Congo DR</t>
+          <t>Scotland - Brazil</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -747,19 +747,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>25/06/2026 03:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Switzerland - Canada</t>
+          <t>Czechia - Mexico</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
         <v>1.2</v>
@@ -844,19 +844,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>25/06/2026 03:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina - Qatar</t>
+          <t>South Africa - South Korea</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>1.2</v>
@@ -941,19 +941,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25/06/2026 00:00</t>
+          <t>25/06/2026 22:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco - Haiti</t>
+          <t>Ecuador - Germany</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>1.2</v>
@@ -1038,19 +1038,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25/06/2026 00:00</t>
+          <t>25/06/2026 22:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scotland - Brazil</t>
+          <t>Curaçao - Ivory Coast</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>1.2</v>
@@ -1135,19 +1135,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25/06/2026 03:00</t>
+          <t>26/06/2026 01:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czechia - Mexico</t>
+          <t>Tunisia - Netherlands</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
@@ -1232,16 +1232,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25/06/2026 03:00</t>
+          <t>26/06/2026 01:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa - South Korea</t>
+          <t>Japan - Sweden</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -1329,16 +1329,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25/06/2026 22:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ecuador - Germany</t>
+          <t>Turkey - United States</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>6</v>
@@ -1426,16 +1426,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25/06/2026 22:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Curaçao - Ivory Coast</t>
+          <t>Paraguay - Australia</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -1523,19 +1523,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26/06/2026 01:00</t>
+          <t>26/06/2026 21:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia - Netherlands</t>
+          <t>Norway - France</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
         <v>1.2</v>
@@ -1620,19 +1620,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26/06/2026 01:00</t>
+          <t>26/06/2026 21:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan - Sweden</t>
+          <t>Senegal - Iraq</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>1.2</v>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>27/06/2026 02:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey - United States</t>
+          <t>Uruguay - Spain</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1814,19 +1814,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>27/06/2026 02:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Paraguay - Australia</t>
+          <t>Cape Verde Islands - Saudi Arabia</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1911,19 +1911,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26/06/2026 21:00</t>
+          <t>27/06/2026 05:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway - France</t>
+          <t>New Zealand - Belgium</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
@@ -2008,19 +2008,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26/06/2026 21:00</t>
+          <t>27/06/2026 05:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Senegal - Iraq</t>
+          <t>Egypt - Iran</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -2105,16 +2105,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>27/06/2026 02:00</t>
+          <t>27/06/2026 23:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uruguay - Spain</t>
+          <t>Panama - England</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
@@ -2202,19 +2202,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27/06/2026 02:00</t>
+          <t>27/06/2026 23:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cape Verde Islands - Saudi Arabia</t>
+          <t>Croatia - Ghana</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>27/06/2026 05:00</t>
+          <t>28/06/2026 01:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New Zealand - Belgium</t>
+          <t>Colombia - Portugal</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
         <v>1.2</v>
@@ -2396,19 +2396,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27/06/2026 05:00</t>
+          <t>28/06/2026 01:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt - Iran</t>
+          <t>Congo DR - Uzbekistan</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>1.2</v>
@@ -2493,19 +2493,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>27/06/2026 23:00</t>
+          <t>28/06/2026 04:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Panama - England</t>
+          <t>Jordan - Argentina</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
         <v>1.2</v>
@@ -2590,19 +2590,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27/06/2026 23:00</t>
+          <t>28/06/2026 04:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia - Ghana</t>
+          <t>Algeria - Austria</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>1.2</v>
@@ -2687,19 +2687,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>28/06/2026 01:30</t>
+          <t>28/06/2026 21:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Colombia - Portugal</t>
+          <t>None - None</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>1.2</v>
@@ -2713,8 +2713,16 @@
       <c r="I24" t="n">
         <v>1.2</v>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>1</t>
@@ -2771,103 +2779,6 @@
         </is>
       </c>
       <c r="W24" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>28/06/2026 01:30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Congo DR - Uzbekistan</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>OVER 1.5</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>UNDER 3.5</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>NOGOAL</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>1X+UNDER</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>0-1 MG</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
         <is>
           <t>0-1 MG</t>
         </is>
